--- a/multiSchoolOutput/03_School_of_Informatics/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/03_School_of_Informatics/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0226_00_GF.Z16</t>
+          <t>0113_00_G.152</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0228_03_3.01</t>
+          <t>0228_07_7.18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1169,7 +1169,7 @@
         <v>291</v>
       </c>
       <c r="F13" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1230,7 +1230,7 @@
         <v>262</v>
       </c>
       <c r="F14" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0214_01_1.10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0113_00_G.14</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0228_11_11.18</t>
+          <t>0201_02_2.04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2084,7 +2084,7 @@
         <v>262</v>
       </c>
       <c r="F28" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0226_01_1.12</t>
+          <t>0227_00_G.05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0214_01_1.10</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4400,7 +4400,7 @@
         <v>291</v>
       </c>
       <c r="F66" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0227_00_G.05</t>
+          <t>0335_01_1.2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4583,7 +4583,7 @@
         <v>300</v>
       </c>
       <c r="F69" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0103_01_1.B09</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0005_00_G.01</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0226_-1_LG.14</t>
+          <t>0450_02_2.55</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0228_-1_LG.09</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0283_01_1.17</t>
+          <t>0113_00_G.14</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0251_01_1.01</t>
+          <t>0201_02_2.11</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0228_11_11.10</t>
+          <t>0450_03_3.35</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7877,7 +7877,7 @@
         <v>270</v>
       </c>
       <c r="F123" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0219_00_G.01</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0228_07_7.18</t>
+          <t>0228_11_11.18</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8731,7 +8731,7 @@
         <v>286</v>
       </c>
       <c r="F137" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -8775,12 +8775,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0228_-1_LG.10</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0008_-1_B.157</t>
+          <t>0251_01_1.02</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0008_02_2.418</t>
+          <t>0003_00_G.03</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0113_02_2.65</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9873,12 +9873,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10422,12 +10422,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0214_01_1.10</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10605,12 +10605,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0227_00_G.02</t>
+          <t>0228_11_11.10</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">

--- a/multiSchoolOutput/03_School_of_Informatics/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/03_School_of_Informatics/solution_weeks_9_10.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +508,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0228_07_7.18</t>
+          <t>0228_03_3.01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0283_01_1.20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -746,7 +746,7 @@
         <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -790,12 +790,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -807,7 +807,7 @@
         <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0201_01_1.06</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1110,7 +1110,7 @@
         <v>291</v>
       </c>
       <c r="F12" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0201_01_1.08</t>
+          <t>0113_01_1.425</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1230,7 +1230,7 @@
         <v>262</v>
       </c>
       <c r="F14" t="n">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0113_00_G.152</t>
+          <t>0226_00_GF.Z16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0214_01_1.10</t>
+          <t>0214_00_G.22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1718,7 +1718,7 @@
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1779,7 +1779,7 @@
         <v>400</v>
       </c>
       <c r="F23" t="n">
-        <v>458</v>
+        <v>307</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0201_02_2.04</t>
+          <t>0112_-1_B.03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1901,7 +1901,7 @@
         <v>400</v>
       </c>
       <c r="F25" t="n">
-        <v>458</v>
+        <v>307</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1962,7 +1962,7 @@
         <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 17:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2206,7 +2206,7 @@
         <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2267,7 +2267,7 @@
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2389,7 +2389,7 @@
         <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0422_J_J.05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0227_00_G.05</t>
+          <t>0226_01_1.12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2755,7 +2755,7 @@
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0201_07_7.14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2999,7 +2999,7 @@
         <v>50</v>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3182,7 +3182,7 @@
         <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3304,7 +3304,7 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3426,7 +3426,7 @@
         <v>116</v>
       </c>
       <c r="F50" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3853,7 +3853,7 @@
         <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3897,12 +3897,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>51</v>
       </c>
       <c r="F58" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3958,12 +3958,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0208_-1_B.1</t>
+          <t>0208_00_G.8</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0201_05_5.07</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4095,7 +4095,7 @@
         <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0113_00_G.09</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4261,12 +4261,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0335_01_1.2</t>
+          <t>0227_00_G.05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0254_01_1.04</t>
+          <t>0219_00_G.01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0226_-1_LG.14</t>
+          <t>0450_02_2.55</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4766,7 +4766,7 @@
         <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4827,7 +4827,7 @@
         <v>400</v>
       </c>
       <c r="F73" t="n">
-        <v>458</v>
+        <v>307</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0228_-1_LG.08</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4949,7 +4949,7 @@
         <v>35</v>
       </c>
       <c r="F75" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4993,12 +4993,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5010,7 +5010,7 @@
         <v>90</v>
       </c>
       <c r="F76" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0313_00_G.10</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5071,7 +5071,7 @@
         <v>30</v>
       </c>
       <c r="F77" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5237,12 +5237,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5254,7 +5254,7 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0283_01_1.20</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5437,7 +5437,7 @@
         <v>45</v>
       </c>
       <c r="F83" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0201_02_2.12</t>
+          <t>0450_02_2.20</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0450_02_2.55</t>
+          <t>0226_-1_LG.14</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0208_00_G.8</t>
+          <t>0227_00_G.06</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5986,7 +5986,7 @@
         <v>86</v>
       </c>
       <c r="F92" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6108,7 +6108,7 @@
         <v>35</v>
       </c>
       <c r="F94" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0227_00_G.05</t>
+          <t>0335_02_2.2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0113_00_G.14</t>
+          <t>0283_01_1.17</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6352,7 +6352,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6413,7 +6413,7 @@
         <v>92</v>
       </c>
       <c r="F99" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0201_02_2.11</t>
+          <t>0113_01_1.434</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6596,7 +6596,7 @@
         <v>52</v>
       </c>
       <c r="F102" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6657,7 +6657,7 @@
         <v>15</v>
       </c>
       <c r="F103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6779,7 +6779,7 @@
         <v>35</v>
       </c>
       <c r="F105" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6823,12 +6823,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6840,7 +6840,7 @@
         <v>8</v>
       </c>
       <c r="F106" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6901,7 +6901,7 @@
         <v>50</v>
       </c>
       <c r="F107" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6962,7 +6962,7 @@
         <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0228_-1_LG.08</t>
+          <t>0300_00_NG.01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7267,7 +7267,7 @@
         <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -7372,12 +7372,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0450_01_1.60</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7389,7 +7389,7 @@
         <v>35</v>
       </c>
       <c r="F115" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0228_-1_LG.10</t>
+          <t>0313_00_G.10</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0450_03_3.35</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0110_02_2.02</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7572,7 +7572,7 @@
         <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7677,12 +7677,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0005_03_3.01</t>
+          <t>0008_02_2.355</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7755,7 +7755,7 @@
         <v>15</v>
       </c>
       <c r="F121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0450_01_1.60</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7938,7 +7938,7 @@
         <v>30</v>
       </c>
       <c r="F124" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0201_01_1.08</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7999,7 +7999,7 @@
         <v>400</v>
       </c>
       <c r="F125" t="n">
-        <v>458</v>
+        <v>307</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -8043,12 +8043,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8060,7 +8060,7 @@
         <v>35</v>
       </c>
       <c r="F126" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -8104,12 +8104,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0450_01_1.60</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8121,7 +8121,7 @@
         <v>30</v>
       </c>
       <c r="F127" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.10</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8182,7 +8182,7 @@
         <v>35</v>
       </c>
       <c r="F128" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8243,7 +8243,7 @@
         <v>15</v>
       </c>
       <c r="F129" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0219_00_G.01</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0228_11_11.18</t>
+          <t>0001_01_1.266</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8548,7 +8548,7 @@
         <v>15</v>
       </c>
       <c r="F134" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0003_01_1.01</t>
+          <t>0112_-1_B.03</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8670,7 +8670,7 @@
         <v>23</v>
       </c>
       <c r="F136" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0227_00_G.02</t>
+          <t>0300_00_NG.01</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0226_-1_LG.10</t>
+          <t>0110_00_G.10</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8853,7 +8853,7 @@
         <v>71</v>
       </c>
       <c r="F139" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0251_01_1.02</t>
+          <t>0003_03_3.01</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0335_00_G.12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9280,7 +9280,7 @@
         <v>15</v>
       </c>
       <c r="F146" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9341,7 +9341,7 @@
         <v>90</v>
       </c>
       <c r="F147" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0003_00_G.03</t>
+          <t>0201_07_7.14</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9707,7 +9707,7 @@
         <v>15</v>
       </c>
       <c r="F153" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9873,12 +9873,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0335_00_G.12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9890,7 +9890,7 @@
         <v>15</v>
       </c>
       <c r="F156" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10073,7 +10073,7 @@
         <v>15</v>
       </c>
       <c r="F159" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10134,7 +10134,7 @@
         <v>51</v>
       </c>
       <c r="F160" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -10178,12 +10178,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10256,7 +10256,7 @@
         <v>30</v>
       </c>
       <c r="F162" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10317,7 +10317,7 @@
         <v>15</v>
       </c>
       <c r="F163" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -10361,12 +10361,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0227_00_G.02</t>
+          <t>0228_11_11.10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10422,12 +10422,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0003_02_2.01</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10605,12 +10605,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0201_03_3.09</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10683,7 +10683,7 @@
         <v>35</v>
       </c>
       <c r="F169" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -10727,12 +10727,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10744,7 +10744,7 @@
         <v>15</v>
       </c>
       <c r="F170" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -10788,12 +10788,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0228_11_11.10</t>
+          <t>0228_-1_LG.08</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
